--- a/docs/ACOLHE_fornecedores.xlsx
+++ b/docs/ACOLHE_fornecedores.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,12 @@
       <name val="Arial"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -119,18 +125,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -139,11 +146,11 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -511,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,292 +544,300 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Ordem sugerida: os dois primeiros valem mais que todos os outros juntos. Um resolve o preço do kit; o outro resolve tudo acima de 240 kits.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ACHADO DE 19/09, depois de varrer 17 novos atacadistas: o Emilio NAO e' caro. O unico atacadista comparavel com preco publico (Paulimar, no Pari, com as MESMAS referencias Minasrey) esta MAIS CARO em todas as linhas comparaveis. Trocar de fornecedor e' um custo de seguranca, nao uma economia — o que ainda pode baratear o kit e' a tabela de revenda do proprio Emilio, que ninguem nunca viu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Contactar</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Porquê este</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>O que isto destrava</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Quanto custa perguntar</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Contactado em</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Resposta</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Emilio (Confecções Emilio)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Hoje ele sozinho fornece 11 das 16 linhas com preço. Os preços que temos são do catálogo aberto — a tabela de revenda nunca foi vista.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>O preço real do kit. Todo o modelo de margem depende desta resposta. Também: pedido mínimo, prazo de pagamento e se ele fatura para PJ nova.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — um e-mail</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Um co-packer (comece pela DirectaLog)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Ninguém publica preço por kit montado. Sem um número, o sistema recusa qualquer lote acima de 240 kits.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>A metade grande do mercado. E o prazo de montagem, que decide se editais de 5 dias são possíveis.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — um e-mail</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Brascol (OneShop Distribuidora)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Preços atrás de login, mas é o único que publica um caminho para BOLETO PARCELADO. Cobre banheira e provavelmente muita coisa do Emilio.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Segunda fonte + a única possibilidade conhecida de comprar a prazo, que é o que muda o ciclo de caixa de 34 dias para ~6.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — cadastro no site</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>JN Fraldas (Mensa Distribuidora)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Fornece as 4 linhas de higiene. Preços públicos, mas de varejo — a tabela de revenda não foi vista.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Desconto nas fraldas e lenços, que são as linhas de consumo mais caras do kit.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — um e-mail</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Yanai Atacado</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Tem a banheira mais barata conforme encontrada (R$17,89) e vende roupas de bebê — pode cobrir linhas do Emilio.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Benchmark de preço nas roupas. Se bater o Emilio, a concentração cai sozinha.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — um e-mail</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Um segundo co-packer com frota própria (COTLOG ou Doma)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Os dois montam kits E são transportadoras. A Doma tem filial em Belém-PA.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Possivelmente o problema do frete inteiro: frete no contrato deles em vez de encomenda a R$150/kit.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — um e-mail</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Um fornecedor da bolsa/mochila do kit</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>A linha kit_enxoval (a própria bolsa) não tem preço nem fornecedor. Municípios costumam querer o brasão impresso.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>A 17ª linha do BOM e o gate do Step 0.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>R$ 0 — pesquisa em curso</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Tenda Atacado</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Só uma linha (sabonete líquido), boleto só à vista, é cash-and-carry.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Pouco. Deixe por último.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>R$ 0</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Regra que você me deu: eu não contacto ninguém sem a sua palavra. Diga 'pode mandar' e eu envio os textos das duas últimas abas para você aprovar antes de sair.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B15:E15"/>
+  <mergeCells count="2">
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -834,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -869,511 +884,1365 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Razão social</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>CNPJ</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>UF / cidade</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Linhas do kit que cobre</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Preços públicos?</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Pedido mínimo</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Pagamento (novo cliente)</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>O que ainda não sabemos</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Contactado em</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Desconto obtido</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Pedido mínimo real</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Prazo pagamento</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Emilio</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>CONFECCOES EMILIO LTDA</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>50.191.584/0001-06</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>SP / São Paulo</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>11 de 16: mochila, banheira, cobertor, cueiro, pagão, body, pano de boca, meias, toalha banho, kit higiene, saboneteira</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Sim (catálogo VTEX aberto)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>https://www.emilio.com.br</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Tabela de revenda, pedido mínimo, prazo, se fatura para CNPJ novo, estoque real. RISCO #15 do registro: 11 linhas num só CNPJ.</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="n"/>
-      <c r="O5" s="6" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Brascol</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>ONESHOP DISTRIBUIDORA LTDA</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>18.483.322/0001-02</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>SP / São Paulo (Brás)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>banheira confirmada; catálogo atrás de login — provável sobreposição ampla com o Emilio</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Não — exige login</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>R$500 atacado / R$1.500 alto atacado</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>PIX, cartão 6x; BOLETO PARCELADO por CNAE</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>https://brascol.com.br</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Tudo além da banheira. Quais CNAEs liberam o boleto parcelado — é o único caminho de crédito conhecido.</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
+      <c r="O6" s="7" t="n"/>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>JN Fraldas</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>MENSA DISTRIBUIDORA LTDA</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>10.290.457/0001-31</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>SP / São Paulo (Canindé)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>4: fralda descartável RN, toalhas umedecidas, shampoo infantil, óleo infantil</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Sim (tier varejo)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>PIX / Visa / Master / Elo</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>https://www.jnfraldas.com.br</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>Se existe tier de revenda. Nenhum caminho para prazo publicado.</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Yanai Atacado</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>COMERCIO DE ROUPAS YANAI LTDA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>44.040.459/0001-94</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>SP / São Paulo</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>banheira (a mais barata conforme: R$17,89); é atacado de ROUPAS — pode cobrir as linhas têxteis</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>https://yanaiatacado.com.br</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>Todo o catálogo têxtil. Esta é a pista mais promissora para quebrar a concentração no Emilio.</t>
         </is>
       </c>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Lar &amp; Cia Utilidades</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>não resolvido</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>SP? (não confirmado)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>banheira e utilidades plásticas</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>https://www.lareciautilidades.com.br</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>O CNPJ não foi encontrado no site. Sem CNPJ não há UF confirmada — e a UF muda o ICMS em ~6 pontos.</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Tenda Atacado</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>TENDA ATACADO SA</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>01.157.555/0011-86</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>SP / Guarulhos</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>1: sabonete líquido</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Boleto À VISTA, cartão</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>https://tendaatacado.com.br</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Pouco a ganhar. Cash-and-carry, sem prazo.</t>
         </is>
       </c>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Martins</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>MARTINS COMERCIO E SERVICOS DE DISTRIBUICAO S/A</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>43.214.055/0001-07</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>MG / Uberlândia</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>banheira</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>https://www.martinsatacado.com.br</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>FORA DE SP: pela LC 123 art. 13 §1 XIII (h) você paga a diferença de ICMS, ~6 pontos. Só vale se for &gt;6% mais barato.</t>
         </is>
       </c>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Paulimar Atacadista</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>PAULIMAR CONFECCOES LTDA</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>60.656.782/0001-43</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo (Pari)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>body, pagão, cueiro, pano de boca, toalha banho, meias; e uma SACOLA de kit a R$49,90</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Sim — sem login</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.paulimar.com.br</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>A melhor segunda fonte têxtil encontrada, e a prova de que o Emilio é barato: mesmas refs Minasrey, preços MAIS ALTOS (pano de boca 2un R$13,75 vs R$5,55 do Emilio). Não tem banheira nem kit higiene.</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>MaxQualy (lojista)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>MAXQUALY ... LTDA</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>53.748.042/0001-71</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>SP / Valinhos</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>shampoo, sabonete líquido, óleo infantil (cosmético/perfumaria; NÃO fralda)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Sim — subdomínio lojista</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>R$ 300,00 — publicado</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>BOLETO 7 DIAS com 2% de desconto — publicado</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>https://lojista.maxqualy.com.br</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>O achado mais importante da varredura, e não é preço: é o SEGUNDO caminho publicado para pagar a prazo em todo o projeto, depois do Brascol — e sem restrição de CNAE. Preços das linhas de bebê não foram lidos um a um.</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Yora Atacado</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YORA ... </t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>00.213.833/0007-26</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>body, pagão, cueiro, pano de boca</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Não — login</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>R$450 online</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.yoraatacado.com.br</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Preços atrás de login. Um cadastro resolve — é a próxima a abrir depois do Brascol.</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>ABC Fraldas</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>GALPAO DAS FRALDAS LTDA</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>41.666.720/0001-78</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>SP / Santo André</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>fralda descartável RN, toalhas umedecidas</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>https://abcfraldas.com.br</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>ATENÇÃO: o site assina 'Abc Fraldas Ltda' mas a razão social na Receita é GALPAO DAS FRALDAS LTDA. Use sempre a razão social em documento de habilitação.</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>7Y Distribuidora</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>7Y DISTRIBUIDORA ...</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>07.018.219/0001-67</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>fralda descartável RN, toalhas umedecidas</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>https://www.7ydistribuidora.com.br</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Nenhum preço publicado em lugar nenhum do site. Segunda fonte de higiene, só por cotação.</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Brindes SP</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>BRINDES SP ...</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>46.033.832/0001-05</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>mochila/bolsa PERSONALIZADA (sublimação, silk, bordado)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Não — só cotação</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>50 unidades</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.brindessp.com.br</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Quando o edital pedir o brasão do município na bolsa, este é o caminho — e o mínimo de 50 peças cabe nos lotes pequenos. Sem preço publicado.</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Mafessoni Baby &amp; Kids</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>MAFESSONI ...</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>96.222.781/0001-38</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SP / Mairiporã</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>body, pagão</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Não — login</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mafessoni.com.br</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Login. Não avaliado.</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="O18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Markha Baby</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>MARKHA ...</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>03.383.226/0001-07</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>body, cobertor</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Pouco lido. Fica como lead.</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="O19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Paravati Atacado</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>PARAVATI ...</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>40.826.972/0001-54</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>não confirmado que tenha enxoval</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Não — login</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de enxoval não confirmada. Lead fraco.</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ISSAM</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ISSAM ...</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>00.327.385/0003-68</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>saboneteira</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Não — login</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Só uma linha, atrás de login.</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Plasútil</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>PLASUTIL ...</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>56.450.877/0001-39</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>banheira, saboneteira</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Não — só cotação</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.000 em mercadoria</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.plasutil.com.br</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>CUIDADO: é o único CNPJ desta lista que a própria empresa não publica no site — veio de diretório e foi confirmado só por razão social. Confirme numa nota fiscal antes de confiar. Mínimo de R$2.000.</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="7" t="n"/>
+      <c r="O22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Era Uma Vez</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ERA UMA VEZ ... (CNAE VAREJISTA)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>38.479.807/0001-21</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SP / São Paulo</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>body, pagão, cobertor — a preço de VAREJO</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.lojaeraumavez.com.br</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>NÃO É ATACADO: CNAE 4781400, varejo. Body R$14,90 contra R$7,56 do Emilio; cobertor R$129,90 contra R$12,15. Serve de teto de preço e de referência de especificação, não de fornecedor.</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Dugu Atacadista</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>VOIGTEX TOALHAS E VARIEDADES LTDA</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>44.073.063/0001-43</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SC / Joinville</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>cueiro, pano de boca, toalha banho — e um KIT ENXOVAL 10 PEÇAS pronto</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>não publicado</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>https://www.duguatacadista.com.br</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>FORA DE SP (~6 pontos de ICMS contra). Mas é o único lugar encontrado que vende um kit enxoval já montado — vale olhar só pela especificação.</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="7" t="n"/>
+      <c r="O24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Luna Baby / Fazendo Arte / Luminati</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>diversos</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ver data/suppliers_shortlist.csv</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>SP, PR, ES</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>bolsa maternidade de consumidor final</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Sim (Luna, Fazendo Arte)</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>FORA DE ORÇAMENTO: o mercado de bolsa maternidade de consumidor começa em R$196,90 e vai a R$745. A mochila do Emilio custa R$52,27. Este não é o mercado certo para essa linha.</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Uma busca por segundas fontes (têxteis, puericultura, higiene e a bolsa do kit) está em andamento; esta aba cresce quando ela terminar.</t>
         </is>
@@ -1409,388 +2278,388 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Esta é a aba que explica por que o Emilio é o e-mail número 1. Quinze das dezassete linhas têm UM fornecedor. Se ele disser não, o kit não existe.</t>
+          <t>Depois da varredura de 19/09: seis linhas ganharam uma segunda fonte com preço legível. Onze continuam com um só preço, e o Emilio sozinho ainda carrega a maioria delas.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Linha do kit</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Fornecedores conhecidos</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Quantos</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Risco</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>banheira_lisa</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Yanai (R$17,89) · Brascol (R$18,05) · Emilio (R$18,90) · Lar &amp; Cia · Martins/MG</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>OK — cinco fontes, spread de 5,6%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>body_manga_longa</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Emilio (R$7,56) · Paulimar (mais caro)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>OK — segunda fonte com preço legível</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>pano_de_boca</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Emilio (R$5,55/3un) · Paulimar (R$13,75/2un)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>OK — mas o Emilio é bem mais barato</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>toalha_banho_infantil</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Emilio (R$10,26/3un) · Paulimar (R$18,38/3un)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>OK — idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>pagao</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Emilio · Paulimar</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>mochila</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Emilio (R$52,27) · Paulimar sacola (R$49,90)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>OK — mas especificações diferentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>cobertor_infantil</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Emilio · (Era Uma Vez só como teto de varejo)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>cobertor_infantil</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE no atacado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>cueiro</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Emilio · Paulimar, Yora, Dugu (sem preço legível)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>cueiro</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>par_de_meias</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Emilio · Paulimar (sem preço legível)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>pagao</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>kit_higiene_bebe</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Emilio — a varredura NÃO achou substituto</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>body_manga_longa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE — categoria mais frágil</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>saboneteira</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Emilio · ISSAM, Plasútil (sem preço)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>pano_de_boca</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>fralda_descartavel_rn</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>JN Fraldas · ABC Fraldas, 7Y (sem preço legível)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>par_de_meias</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>toalhas_umedecidas</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>JN Fraldas · ABC Fraldas, 7Y (sem preço)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>toalha_banho_infantil</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>shampoo_infantil</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>JN Fraldas · MaxQualy (boleto 7 dias!)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>kit_higiene_bebe</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>oleo_infantil</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>JN Fraldas · MaxQualy</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>saboneteira</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Emilio</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>sabonete_liquido</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Tenda Atacado · MaxQualy</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>fralda_descartavel_rn</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>JN Fraldas</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>toalhas_umedecidas</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>JN Fraldas</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>shampoo_infantil</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>JN Fraldas</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>oleo_infantil</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>JN Fraldas</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>sabonete_liquido</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Tenda Atacado</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>ÚNICA FONTE</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ÚNICA FONTE com preço</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>kit_enxoval (a bolsa)</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>nenhum</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Dugu/SC vende um kit 10 peças pronto — sem preço lido</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>SEM PREÇO E SEM FORNECEDOR — trava o gate do Step 0</t>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>AINDA SEM PREÇO — trava o gate do Step 0</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Emilio sozinho:</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>11 das 16 linhas com preço</t>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>11 das 16 linhas com preço — e a varredura confirmou que ele é o mais barato</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Fonte: data/cost_table.csv, data/cost_banheira.csv, data/cost_toiletries.csv, docs/RISK_REGISTER.md risco #15.</t>
+          <t>Fonte: data/cost_table.csv, cost_banheira.csv, cost_toiletries.csv, suppliers_shortlist.csv, RISK_REGISTER #15.</t>
         </is>
       </c>
     </row>
@@ -1837,790 +2706,790 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Razão social</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>CNPJ</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Por que este</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Mínimo publicado</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Embarca no frete dele?</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Contactado em</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Preço por kit</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Prazo (dias)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>DirectaLog</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>DIRECTALOG LOGISTICA LTDA</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>22.932.742/0001-98</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Osasco/SP</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Sem mínimo, cobrança por serviço, preparo em D+3, confere XML contra o físico, nomeia Correios/Jadlog/Total Express. O perfil mais próximo do que você precisa.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>sem mínimo</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Sim — retribui tabela das transportadoras</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>https://www.directalog.com.br</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>VIP Manuseios</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>não impresso no site — UNVERIFIED</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>'Sem volume mínimo'. Confere por NF com relatório por NF e saldo em tempo real — exatamente o controlo que você precisa recebendo de 4 atacadistas.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>sem mínimo</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Sim — cota junto aos Correios</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>https://www.vipmanuseios.com.br</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>COTLOG</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>COTLOG SOLUCOES LOGISTICAS LTDA</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>10.273.317/0001-55</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Cotia/SP</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Monta kits E é transportadora própria (rodoviário fracionado + aéreo, porta a porta). ISO 9001. Pode resolver o frete junto com a montagem.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Sim — frota/contrato próprios</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>https://www.cotlog.com.br/montagem-kits</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Doma Logística</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>DOMA LOGISTICA LTDA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>27.541.681/0001-51</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Guarulhos/SP</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Frota própria e FILIAL EM BELÉM-PA — a única com presença publicada no Norte/Nordeste, que é onde estão os editais que valem a pena.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Sim — frota própria</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>https://www.domalogistica.com.br</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>UP! Manuseios</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>UP ORGANIZACAO E EVENTOS LTDA</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>43.213.105/0001-31</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Único com capacidade PROVADA publicada: 7.500 kits em 10 dias úteis, paletizados. É a referência para um lote grande.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Sim — Correios/transportadora/carro dedicado</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>https://www.upmanuseios.com.br</t>
         </is>
       </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>DRENG</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>DRENG SOLUCOES E TECNOLOGIA EM LOGISTICA LTDA</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>48.878.504/0001-35</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Publica que tem tabela de preços pré-fixada com desconto progressivo e sem contrato longo. Deve responder rápido com número.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>não declarado</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>https://www.dreng.com.br</t>
         </is>
       </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>G+Ship (Guarde Mais)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>ROGER FULFILLMENT LTDA</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>46.373.347/0001-80</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Sem mínimo e tem simulador de preço no site. Mas o transporte é por sua conta.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>sem mínimo</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Não — transporte é do cliente</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>https://goship.com.br</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Tempos</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>TEMPOS DE BRASIL TERCEIRIZACAO... LTDA</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>01.211.578/0001-50</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Santana de Parnaíba/SP</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Co-packer industrial desde 1996, 2.000 m², ISO 9001:2015. Para o cenário de 5.000 kits.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>não declarado</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>https://www.tempos.com.br/co-packer</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Mão na Massa</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>MAO NA MASSA PRODUCOES LTDA</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>26.195.320/0001-38</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Montagem + armazenagem, despacho por Correios ou motoboy. Segunda onda.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Sim — Correios</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>https://www.maonamassamanuseios.com.br</t>
         </is>
       </c>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Envio Certo</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>ENVIO CERTO PRODUCOES E SERVICOS LTDA</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>43.628.686/0001-72</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>CNAE 8292-0/00 (envasamento e empacotamento sob contrato) — é literalmente a atividade. Foco em kits de influencer.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Sim — com rastreio nacional</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>https://www.enviocertomanuseios.com.br</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Teconlog</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>TECONLOG SOLUCOES LOGISTICAS LTDA</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>22.027.337/0001-25</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Vargem Grande Paulista/SP</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>7.000 m², 6.000 posições-palete, expedição D+0. Grande — pode não querer um cliente pequeno.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Parceiros homologados</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>https://teconlog.com.br</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Paulista Express</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>PAULISTA EXPRESS TRANSPORTES LTDA</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>74.289.034/0001-84</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>São Bernardo do Campo/SP</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Transportadora com frota própria que também monta kits — mas a cobertura publicada é só SP capital e interior.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Sim — frota própria (só SP)</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>https://www.paulistaexpress.com.br</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Contacto Logística</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>não impresso no site — UNVERIFIED</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>São Paulo/SP</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Publica 'poucas unidades ou grandes quantidades'. CNPJ não confirmado.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>sem mínimo</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>não declarado</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>https://contactologistica.com.br</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Grupo SRM</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>SRM - TERCEIRIZACAO DE SERVICOS E RECURSOS HUMANOS LTDA</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>02.798.885/0001-41</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Barueri/SP</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>ATENÇÃO: vende MÃO DE OBRA por peça montada, não é armazém. Isso pode esbarrar na regra C3 (sem funcionários). Só como último recurso e com o contador a confirmar.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>não publicado</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>https://www.gruposrm.com.br</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>NÃO contactar: Nascra Brindes — CNPJ com situação SUSPENSA na Receita.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Fora de perfil: FM Logistic (só grandes contas), Saberpack (envase de alimentos/químicos), Cartlog (endereço em Londrina/PR), LJ Indústria (CNPJ não impresso).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Não são co-packers: Mercado Livre Full, Amazon FBA, Magalu, Shopee — só montam pedidos das próprias plataformas.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Sites bloqueados na pesquisa (podem valer uma olhada manual): Lotus Logística, MPP Log/Promopack, DHL Fulfillment, Frenet.</t>
         </is>
@@ -2665,232 +3534,232 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Assunto: Cadastro de revenda — kits de enxoval para prefeituras (CNPJ em SP)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11" t="n"/>
+      <c r="B5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bom dia,</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Sou [SEU NOME], da [EMPRESA], em São Paulo. Montamos kits de enxoval para</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>recém-nascidos e fornecemos para prefeituras através de licitação pública</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>(pregão eletrônico). Compramos o kit completo — roupas, enxoval, higiene,</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>banheira e bolsa — e entregamos montado ao município.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Gostaria de abrir cadastro de revenda e receber a tabela de atacado.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Algumas perguntas objetivas:</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>1. Qual a tabela de preços para revenda/atacado nos itens abaixo, e como ela</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   se compara ao preço do site?</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">      - [colar aqui a lista de itens e as quantidades típicas]</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>2. Existe pedido mínimo, por valor ou por peça? E pedido mínimo por SKU?</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>3. Condições de pagamento para cliente novo: só PIX/cartão, ou existe caminho</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   para boleto a prazo? Em quantos pedidos ou em quanto tempo?</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11" t="n"/>
+      <c r="B24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>4. Como funciona o faturamento para CNPJ? Emitem NF-e com os dados do meu</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   pedido de compra?</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>5. Vocês conseguem reservar/segurar estoque entre a assinatura de um contrato</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   público e a compra? Nosso ciclo é: ganhamos a licitação, recebemos a nota</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   de empenho e só então compramos — normalmente com 5 a 20 dias para entregar.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>6. Entregam num endereço de terceiros em São Paulo (empresa que monta os kits)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   ou só no endereço de cadastro?</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="n"/>
+      <c r="B34" s="12" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>7. Qual o prazo de entrega para São Paulo capital, num pedido de [X] peças?</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="n"/>
+      <c r="B36" s="12" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Sou uma operação pequena e nova — não vou prometer volume que ainda não tenho.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>O que posso dizer é que cada contrato ganho é uma compra fechada, do kit</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>inteiro, e que preciso de um fornecedor com preço estável para conseguir</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>precificar uma proposta com 12 meses de validade.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="11" t="n"/>
+      <c r="B41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Obrigado pela atenção,</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>[SEU NOME] — [EMPRESA] — CNPJ [xx] — [telefone] — [e-mail]</t>
         </is>
@@ -2943,239 +3812,239 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Assunto: Cotação — montagem de kits de enxoval (lotes de 100 a 5.000)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11" t="n"/>
+      <c r="B5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bom dia,</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="11" t="n"/>
+      <c r="B7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Sou [SEU NOME], da [EMPRESA], em São Paulo. Fornecemos kits de enxoval para</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>recém-nascidos a prefeituras, por licitação. Preciso de um parceiro para</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>receber a mercadoria de 3 a 6 atacadistas do Brás/Pari, montar os kits e</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>expedir para o município.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Cada kit tem 17 a 20 itens: roupas de bebê, toalhas, banheira plástica de</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>20 litros, itens de higiene e uma bolsa. A embalagem final é a própria bolsa</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>do kit, dentro de caixa de papelão.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>1. Preço por kit montado para lotes de 100, 500 e 5.000 kits. Há adicional</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   por item volumoso (a banheira)?</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>2. Cobram por kit, por hora ou por peça? Há taxa de setup, mínimo de</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   faturamento ou mensalidade?</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>3. Recebem entregas de 3 a 6 fornecedores distintos para o mesmo projeto?</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   Conferem contra as NF-e? Como e em quanto tempo reportam faltas e avarias?</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>4. Quantos dias de armazenagem sem custo entre o primeiro recebimento e a</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   expedição? Preço por posição-palete/dia além disso?</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>5. Prazo de montagem em dias úteis, contado do recebimento do último item,</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   para 100 / 500 / 5.000 kits.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>6. Expedição: emitem CT-e em nome de vocês (frete no contrato de vocês) ou</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   reservam no meu CNPJ? Quais transportadoras? Peço cotação de um lote</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   paletizado de São Paulo para Recife, Fortaleza, Salvador, Belém e um</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   município do interior do Nordeste, para 100 e 500 kits. Há ad valorem ou</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   GRIS sobre um kit de ~R$ 200?</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>7. Entrega em órgão público: aceitam entrega agendada com conferência do</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   recebedor, canhoto assinado e comprovante para o processo de pagamento?</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>8. Condições de pagamento: sinal na aprovação? boleto 14/28 dias? faturam</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   separado a montagem (NFS-e) e o frete (CT-e)?</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>9. Seguro da mercadoria em armazém e em trânsito — quem cobre e até que valor?</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>10. Cadastro: exigem tempo mínimo de CNPJ, faturamento mínimo ou referências?</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="11" t="n"/>
+      <c r="B38" s="12" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Obrigado,</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>[SEU NOME] — [EMPRESA] — CNPJ [xx] — [telefone] — [e-mail]</t>
         </is>
